--- a/variance_templates.xlsx
+++ b/variance_templates.xlsx
@@ -1,76 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\LINK TEST\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7959D7E6-EFE5-4C31-998D-B8CB2959CD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Templates" sheetId="1" r:id="rId1"/>
+    <sheet name="Templates" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Template Name</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>FRndz</t>
-  </si>
-  <si>
-    <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;;Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
-  </si>
-  <si>
-    <t>lka-3plcssops8@efl.global</t>
-  </si>
-  <si>
-    <t>EGF</t>
-  </si>
-  <si>
-    <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
-  </si>
-  <si>
-    <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
-  </si>
-  <si>
-    <t>PFC</t>
-  </si>
-  <si>
-    <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -89,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -391,54 +408,167 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="3" width="50" customWidth="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EGF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FRndz</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lka-3plcssops8@efl.global</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GAMMA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MASK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MASKTR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MKOO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/variance_templates.xlsx
+++ b/variance_templates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -441,80 +441,80 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EGF</t>
+          <t>BIAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
+          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EMJ</t>
+          <t>EGF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FRndz</t>
+          <t>EMJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
+          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lka-3plcssops8@efl.global</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GAMMA</t>
+          <t>FRndz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>lka-3plcssops8@efl.global</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MASK</t>
+          <t>GAMMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
+          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -526,12 +526,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MASKTR</t>
+          <t>IGPL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+          <t>"Shamima Firoz" &lt;shamimaf@efl.global&gt;"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -543,12 +543,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MKOO</t>
+          <t>JYJY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+          <t>"Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -560,15 +560,100 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Sandakelum Dissanayake" &lt;Sandaked@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MASK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MASKTR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MKOO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>PFC</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SOFTL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Adikari" &lt;adikarid@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/variance_templates.xlsx
+++ b/variance_templates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -441,46 +441,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BIAL</t>
+          <t>ACME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
+          <t>Dedunu Ganhewa &lt;dedunug@efl.global&gt;; Akash Mithuna &lt;lka-3plcssops8@efl.global&gt;; Hashitha Shashen &lt;Lka-3plcssops7@efl.global&gt;; Hasitha Kuruvitage &lt;hasithaku@efl.global&gt;; Harsha Prabodana &lt;harshap@efl.global&gt;; Anushi Hewamaraba &lt;anushih@efl.global&gt;; Hirusha Nimasara &lt;lka-softlogicops@efl.global&gt;; Shamima Firoz &lt;shamimaf@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; Prabodhi Sethsarani Peiris &lt;Prabodhip@efl.global&gt;; LPPL GRN GDN &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EGF</t>
+          <t>BIAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
+          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EMJ</t>
+          <t>BRIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
+          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -492,46 +492,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FRndz</t>
+          <t>DRDNS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
+          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lka-3plcssops8@efl.global</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GAMMA</t>
+          <t>EGF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IGPL</t>
+          <t>EMJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"Shamima Firoz" &lt;shamimaf@efl.global&gt;"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
+          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -543,29 +543,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JYJY</t>
+          <t>FRndz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;</t>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>lka-3plcssops8@efl.global</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>GAMMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Sandakelum Dissanayake" &lt;Sandaked@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;</t>
+          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MASK</t>
+          <t>IGPL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
+          <t>"Shamima Firoz" &lt;shamimaf@efl.global&gt;"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -594,12 +594,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MASKTR</t>
+          <t>JYJY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+          <t>"Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -611,12 +611,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MKOO</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Sandakelum Dissanayake" &lt;Sandaked@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -628,28 +628,96 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>MASK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>MASKRE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Adeesha Fernando &lt;adishaf@efl.global&gt;; Kawshalya Parameshwaran &lt;lka-3plcssops13@efl.global&gt;; Dedunu Ganhewa &lt;dedunug@efl.global&gt;; Chiran Hansaka &lt;chiranh@efl.global&gt;; Pushpa Kumara &lt;kumarag@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Kandana-FC &lt;lka-hwe2e@efl.global&gt;; KFC Intimo &lt;lka-kfcintimo@efl.global&gt;; KFC Inbound &lt;lka-kfcinbound@efl.global&gt;; Shifan Mohamed &lt;shifanm@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Sanjaya Perera &lt;sanjayap@efl.global&gt;; Priyantha Sanjeewa &lt;priyanthas@efl.global&gt;; Rasika Mallawarachchi &lt;rasikam@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; Ishini Jayakodi &lt;ishinij@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MASKTR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MKOO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>SOFTL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Adikari" &lt;adikarid@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>

--- a/variance_templates.xlsx
+++ b/variance_templates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -458,29 +458,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BIAL</t>
+          <t>BDXAP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
+          <t>Hasitha Kuruvitage &lt;hasithaku@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Amila Saman &lt;lka-3plcssops5@efl.global&gt;; LPPL GRN GDN &lt;lka-lppl-grngdn@efl.global&gt;; PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRIN</t>
+          <t>BIAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
+          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -492,12 +492,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DRDNS</t>
+          <t>BRIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
+          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -509,80 +509,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EGF</t>
+          <t>DRDNS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
+          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMJ</t>
+          <t>EGF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRndz</t>
+          <t>EMJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
+          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lka-3plcssops8@efl.global</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GAMMA</t>
+          <t>FRndz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>lka-3plcssops8@efl.global</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IGPL</t>
+          <t>GAMMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"Shamima Firoz" &lt;shamimaf@efl.global&gt;"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
+          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -594,12 +594,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JYJY</t>
+          <t>HMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;</t>
+          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hasitha Kuruvitage" &lt;hasithaku@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Chanuka Rathnayake" &lt;chanukar@efl.global&gt;</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -611,12 +611,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>IGPL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Sandakelum Dissanayake" &lt;Sandaked@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;</t>
+          <t>"Shamima Firoz" &lt;shamimaf@efl.global&gt;"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -628,12 +628,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MASK</t>
+          <t>JYJY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
+          <t>"Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -645,29 +645,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MASKRE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adeesha Fernando &lt;adishaf@efl.global&gt;; Kawshalya Parameshwaran &lt;lka-3plcssops13@efl.global&gt;; Dedunu Ganhewa &lt;dedunug@efl.global&gt;; Chiran Hansaka &lt;chiranh@efl.global&gt;; Pushpa Kumara &lt;kumarag@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Kandana-FC &lt;lka-hwe2e@efl.global&gt;; KFC Intimo &lt;lka-kfcintimo@efl.global&gt;; KFC Inbound &lt;lka-kfcinbound@efl.global&gt;; Shifan Mohamed &lt;shifanm@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Sanjaya Perera &lt;sanjayap@efl.global&gt;; Priyantha Sanjeewa &lt;priyanthas@efl.global&gt;; Rasika Mallawarachchi &lt;rasikam@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; Ishini Jayakodi &lt;ishinij@efl.global&gt;</t>
+          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Sandakelum Dissanayake" &lt;Sandaked@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MASKTR</t>
+          <t>MASK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -679,47 +679,115 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MKOO</t>
+          <t>MASKRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+          <t>Adeesha Fernando &lt;adishaf@efl.global&gt;; Kawshalya Parameshwaran &lt;lka-3plcssops13@efl.global&gt;; Dedunu Ganhewa &lt;dedunug@efl.global&gt;; Chiran Hansaka &lt;chiranh@efl.global&gt;; Pushpa Kumara &lt;kumarag@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Kandana-FC &lt;lka-hwe2e@efl.global&gt;; KFC Intimo &lt;lka-kfcintimo@efl.global&gt;; KFC Inbound &lt;lka-kfcinbound@efl.global&gt;; Shifan Mohamed &lt;shifanm@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Sanjaya Perera &lt;sanjayap@efl.global&gt;; Priyantha Sanjeewa &lt;priyanthas@efl.global&gt;; Rasika Mallawarachchi &lt;rasikam@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; Ishini Jayakodi &lt;ishinij@efl.global&gt;</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>MASKTR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>MKOO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SGLLP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>"Prabodhi Sethsarani Peiris" &lt;Prabodhip@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "Hasitha Kuruvitage" &lt;hasithaku@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "'Dhanushka Adikaram'" &lt;dhanushkaa@efl.global&gt;; "Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Dilshan Perera" &lt;dhanukap@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Lakshitha Gayan" &lt;lakshithag@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;; "Dinindu Madushanka" &lt;dinindum@efl.global&gt;; "Sanduni Chathurangani" &lt;Sandunic@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>SOFTL</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Adikari" &lt;adikarid@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPAR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"Prabodhi Sethsarani Peiris" &lt;Prabodhip@efl.global&gt;; "Sampath Ekanayake" &lt;sampathe@efl.global&gt;; "Theekshana Akalanka" &lt;takalanka@efl.global&gt;; "Hasitha Kodithuwakku" &lt;hasithakod@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>"Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Ashan Dilentha" &lt;ashand@efl.global&gt;; "Samith Kanishka" &lt;samithk@efl.global&gt;; "Asitha Samalka" &lt;lka-3plcssops11@efl.global&gt;; "Tharindu Sandaruwan" &lt;tharindus@efl.global&gt;; "Salinda Madushan" &lt;salindam@efl.global&gt;; "Namith Rajapakse" &lt;namithr@efl.global&gt;; "GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>

--- a/variance_templates.xlsx
+++ b/variance_templates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -730,42 +730,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>NINDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; LPPL GRN GDN &lt;lka-lppl-grngdn@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Dilmi Weerathunga &lt;lka-oiu-intern4@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SGLLP</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"Prabodhi Sethsarani Peiris" &lt;Prabodhip@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "Hasitha Kuruvitage" &lt;hasithaku@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "'Dhanushka Adikaram'" &lt;dhanushkaa@efl.global&gt;; "Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Dilshan Perera" &lt;dhanukap@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Lakshitha Gayan" &lt;lakshithag@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;; "Dinindu Madushanka" &lt;dinindum@efl.global&gt;; "Sanduni Chathurangani" &lt;Sandunic@efl.global&gt;</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
-        </is>
-      </c>
+          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOFTL</t>
+          <t>SGLLP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Adikari" &lt;adikarid@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
+          <t>"Prabodhi Sethsarani Peiris" &lt;Prabodhip@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "Hasitha Kuruvitage" &lt;hasithaku@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "'Dhanushka Adikaram'" &lt;dhanushkaa@efl.global&gt;; "Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Dilshan Perera" &lt;dhanukap@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Lakshitha Gayan" &lt;lakshithag@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;; "Dinindu Madushanka" &lt;dinindum@efl.global&gt;; "Sanduni Chathurangani" &lt;Sandunic@efl.global&gt;</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -777,15 +777,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>SOFTL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Adikari" &lt;adikarid@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>SPAR</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>"Prabodhi Sethsarani Peiris" &lt;Prabodhip@efl.global&gt;; "Sampath Ekanayake" &lt;sampathe@efl.global&gt;; "Theekshana Akalanka" &lt;takalanka@efl.global&gt;; "Hasitha Kodithuwakku" &lt;hasithakod@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>"Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Ashan Dilentha" &lt;ashand@efl.global&gt;; "Samith Kanishka" &lt;samithk@efl.global&gt;; "Asitha Samalka" &lt;lka-3plcssops11@efl.global&gt;; "Tharindu Sandaruwan" &lt;tharindus@efl.global&gt;; "Salinda Madushan" &lt;salindam@efl.global&gt;; "Namith Rajapakse" &lt;namithr@efl.global&gt;; "GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>

--- a/variance_templates.xlsx
+++ b/variance_templates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -458,12 +458,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BDXAP</t>
+          <t>BALTD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hasitha Kuruvitage &lt;hasithaku@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Amila Saman &lt;lka-3plcssops5@efl.global&gt;; LPPL GRN GDN &lt;lka-lppl-grngdn@efl.global&gt;; PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;</t>
+          <t>Harsha Prabodana &lt;harshap@efl.global&gt;; Amila Saman &lt;lka-3plcssops5@efl.global&gt;; LPPL GRN GDN &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -475,29 +475,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BIAL</t>
+          <t>BDXAP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
+          <t>Hasitha Kuruvitage &lt;hasithaku@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Amila Saman &lt;lka-3plcssops5@efl.global&gt;; LPPL GRN GDN &lt;lka-lppl-grngdn@efl.global&gt;; PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRIN</t>
+          <t>BIAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
+          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -509,12 +509,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRDNS</t>
+          <t>BRIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
+          <t>"Harsha Prabodana" &lt;harshap@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -526,80 +526,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EGF</t>
+          <t>DRDNS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
+          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMJ</t>
+          <t>EGF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; lka-egf-grngdn &lt;lka-egf-grngdn@efl.global&gt;; HID Inbound 1 &lt;lka-hidinbound-1@efl.global&gt;; EGF Operations &lt;lka-egfops@efl.global&gt;; HID Centralized Operations &lt;lka-hidCentralizedOps@efl.global&gt;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FRndz</t>
+          <t>EMJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
+          <t>"Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lka-3plcssops8@efl.global</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GAMMA</t>
+          <t>FRndz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>lka-3plcssops8@efl.global</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HMS</t>
+          <t>GAMMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hasitha Kuruvitage" &lt;hasithaku@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Chanuka Rathnayake" &lt;chanukar@efl.global&gt;</t>
+          <t>"Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -611,12 +611,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IGPL</t>
+          <t>HMS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"Shamima Firoz" &lt;shamimaf@efl.global&gt;"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
+          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hasitha Kuruvitage" &lt;hasithaku@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Chanuka Rathnayake" &lt;chanukar@efl.global&gt;</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -628,12 +628,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JYJY</t>
+          <t>IGPL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;</t>
+          <t>"Shamima Firoz" &lt;shamimaf@efl.global&gt;"Harsha Prabodana" &lt;harshap@efl.global&gt;</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -645,12 +645,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>JYJY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Sandakelum Dissanayake" &lt;Sandaked@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;</t>
+          <t>"Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Adeesha Fernando" &lt;adishaf@efl.global&gt;</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -662,12 +662,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MASK</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
+          <t>"Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Sandakelum Dissanayake" &lt;Sandaked@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -679,46 +679,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MASKRE</t>
+          <t>MASK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adeesha Fernando &lt;adishaf@efl.global&gt;; Kawshalya Parameshwaran &lt;lka-3plcssops13@efl.global&gt;; Dedunu Ganhewa &lt;dedunug@efl.global&gt;; Chiran Hansaka &lt;chiranh@efl.global&gt;; Pushpa Kumara &lt;kumarag@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Kandana-FC &lt;lka-hwe2e@efl.global&gt;; KFC Intimo &lt;lka-kfcintimo@efl.global&gt;; KFC Inbound &lt;lka-kfcinbound@efl.global&gt;; Shifan Mohamed &lt;shifanm@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Sanjaya Perera &lt;sanjayap@efl.global&gt;; Priyantha Sanjeewa &lt;priyanthas@efl.global&gt;; Rasika Mallawarachchi &lt;rasikam@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; Ishini Jayakodi &lt;ishinij@efl.global&gt;</t>
+          <t>"Dilmi Weerathunga" &lt;lka-oiu-intern4@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Ishini Jayakodi" &lt;ishinij@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "lka-pfc-grngdn" &lt;lka-pfc-grngdn@efl.global&gt;</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MASKTR</t>
+          <t>MASKRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+          <t>Adeesha Fernando &lt;adishaf@efl.global&gt;; Kawshalya Parameshwaran &lt;lka-3plcssops13@efl.global&gt;; Dedunu Ganhewa &lt;dedunug@efl.global&gt;; Chiran Hansaka &lt;chiranh@efl.global&gt;; Pushpa Kumara &lt;kumarag@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Kandana-FC &lt;lka-hwe2e@efl.global&gt;; KFC Intimo &lt;lka-kfcintimo@efl.global&gt;; KFC Inbound &lt;lka-kfcinbound@efl.global&gt;; Shifan Mohamed &lt;shifanm@efl.global&gt;; Dinith Chandrasiri &lt;dinithc@efl.global&gt;; Sanjaya Perera &lt;sanjayap@efl.global&gt;; Priyantha Sanjeewa &lt;priyanthas@efl.global&gt;; Rasika Mallawarachchi &lt;rasikam@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; Ishini Jayakodi &lt;ishinij@efl.global&gt;</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MKOO</t>
+          <t>MASKTR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -730,59 +730,59 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NINDA</t>
+          <t>MKOO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; LPPL GRN GDN &lt;lka-lppl-grngdn@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Dilmi Weerathunga &lt;lka-oiu-intern4@efl.global&gt;</t>
+          <t>"Asha Nishadi" &lt;nishadia@efl.global&gt;; "Tharindu Ishara" &lt;lka-3plcssops1@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Kavindu Somarathna" &lt;kavindus@efl.global&gt;; "Dilmi Kawindya" &lt;LKA-Warehouse@efl.global&gt;; "Madushani Fonseka" &lt;madushanif@efl.global&gt;; "Praveen Danasiri" &lt;praveend@efl.global&gt;; "Subhash Madhusanka" &lt;msubash@efl.global&gt;; "Kavindu Ravishan" &lt;kavindur@efl.global&gt;; "Chathuranga Lakshan" &lt;LKA-Crossorder5@efl.global&gt;; "PFC Fabric Operation" &lt;lka-pfc-fabricops@efl.global&gt;; "Dulanjali Kumari" &lt;dulanjalik@efl.global&gt;; "Samitha Preshan" &lt;samithapr@efl.global&gt;; "Ishara Madusanka Ovitigala" &lt;isharao@efl.global&gt;; "amantepfc@gmail.com" &lt;amantepfc@gmail.com&gt;</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>NINDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Amila Saman &lt;lka-3plcssops5@efl.global&gt;; LPPL GRN GDN &lt;lka-lppl-grngdn@efl.global&gt;; Asha Nishadi &lt;nishadia@efl.global&gt;; PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Dilmi Weerathunga &lt;lka-oiu-intern4@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GRN GDN Team &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SGLLP</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"Prabodhi Sethsarani Peiris" &lt;Prabodhip@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "Hasitha Kuruvitage" &lt;hasithaku@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "'Dhanushka Adikaram'" &lt;dhanushkaa@efl.global&gt;; "Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Dilshan Perera" &lt;dhanukap@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Lakshitha Gayan" &lt;lakshithag@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;; "Dinindu Madushanka" &lt;dinindum@efl.global&gt;; "Sanduni Chathurangani" &lt;Sandunic@efl.global&gt;</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
-        </is>
-      </c>
+          <t>PFC Fabric Operation &lt;lka-pfc-fabricops@efl.global&gt;; Tharindu Ishara &lt;lka-3plcssops1@efl.global&gt;; Madushani Fonseka &lt;madushanif@efl.global&gt;; Dilmi Kawindya &lt;LKA-Warehouse@efl.global&gt;; Chathuranga Lakshan &lt;LKA-Crossorder5@efl.global&gt;; Kavindu Ravishan &lt;kavindur@efl.global&gt;; Samitha Preshan &lt;samithapr@efl.global&gt;; Ishara Madusanka Ovitigala &lt;isharao@efl.global&gt;; Praveen Danasiri &lt;praveend@efl.global&gt;; Dulanjali Kumari &lt;dulanjalik@efl.global&gt;; Subhash Madhusanka &lt;msubash@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOFTL</t>
+          <t>SGLLP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Adikari" &lt;adikarid@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
+          <t>"Prabodhi Sethsarani Peiris" &lt;Prabodhip@efl.global&gt;; "Rasheeq Thamsy" &lt;lka-3plcssops9@efl.global&gt;; "Hasitha Kuruvitage" &lt;hasithaku@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "'Dhanushka Adikaram'" &lt;dhanushkaa@efl.global&gt;; "Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Dilshan Perera" &lt;dhanukap@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Asha Nishadi" &lt;nishadia@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Lakshitha Gayan" &lt;lakshithag@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;; "Dinindu Madushanka" &lt;dinindum@efl.global&gt;; "Sanduni Chathurangani" &lt;Sandunic@efl.global&gt;</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -794,15 +794,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>SOFTL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>"Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;; "Dhanuka Adikari" &lt;adikarid@efl.global&gt;; "Hashitha Shashen" &lt;Lka-3plcssops7@efl.global&gt;; "Harsha Prabodana" &lt;harshap@efl.global&gt;; "Dedunu Ganhewa" &lt;dedunug@efl.global&gt;; "Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Hirusha Nimasara" &lt;lka-softlogicops@efl.global&gt;; "Shamima Firoz" &lt;shamimaf@efl.global&gt;; "Dashini Dharmadasa" &lt;dashinid@efl.global&gt;; "Demintha Lakshan" &lt;Lakshann@efl.global&gt;; "Ishara Samarasinghe" &lt;lka-OIU-intern2@efl.global&gt;; "Charaki Dilakshi" &lt;charakid@efl.global&gt;; "LPPL GRN GDN" &lt;lka-lppl-grngdn@efl.global&gt;; "Malithi Paboda Sewwandi" &lt;lka-oiu-intern5@efl.global&gt;</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>"GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>SPAR</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>"Prabodhi Sethsarani Peiris" &lt;Prabodhip@efl.global&gt;; "Sampath Ekanayake" &lt;sampathe@efl.global&gt;; "Theekshana Akalanka" &lt;takalanka@efl.global&gt;; "Hasitha Kodithuwakku" &lt;hasithakod@efl.global&gt;; "Kavindika Gayathri" &lt;lka-3plcssops12@efl.global&gt;; "Nuwangi Wijesena" &lt;nuwangiw@efl.global&gt;</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>"Anushi Hewamaraba" &lt;anushih@efl.global&gt;; "Ashan Dilentha" &lt;ashand@efl.global&gt;; "Samith Kanishka" &lt;samithk@efl.global&gt;; "Asitha Samalka" &lt;lka-3plcssops11@efl.global&gt;; "Tharindu Sandaruwan" &lt;tharindus@efl.global&gt;; "Salinda Madushan" &lt;salindam@efl.global&gt;; "Namith Rajapakse" &lt;namithr@efl.global&gt;; "GRN GDN Team" &lt;lka-grngdnteam@efl.global&gt;</t>
         </is>
